--- a/output/result/Result_solved.xlsx
+++ b/output/result/Result_solved.xlsx
@@ -1068,10 +1068,10 @@
         <v>15</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>7210</v>
+        <v>5210</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>28</v>
+        <v>228</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>225</v>
@@ -1100,10 +1100,10 @@
         <v>15</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>7210</v>
+        <v>5210</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>18</v>
+        <v>218</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>215</v>
